--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487776_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487776_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4652</v>
+        <v>2.45</v>
       </c>
       <c r="E2" t="n">
-        <v>7.109</v>
+        <v>3.9176</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6438</v>
+        <v>-1.4676</v>
       </c>
       <c r="G2" t="n">
         <v>0.3031</v>
@@ -610,13 +610,13 @@
         <v>2.7055</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7885</v>
+        <v>1.7733</v>
       </c>
       <c r="T2" t="n">
-        <v>4.9288</v>
+        <v>1.7374</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1402</v>
+        <v>0.0359</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2914</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07829999999999999</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1141</v>
+        <v>1.0549</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1925</v>
+        <v>-1.1399</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3363</v>
+        <v>-0.3658</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4604</v>
+        <v>-0.1258</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1241</v>
+        <v>-0.24</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5237000000000001</v>
+        <v>0.7692</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6804</v>
+        <v>0.6908</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1568</v>
+        <v>0.0784</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8126</v>
+        <v>-1.1349</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.78</v>
+        <v>-0.8165</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0326</v>
+        <v>-0.3184</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1253</v>
+        <v>0.3859</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5905</v>
+        <v>0.0557</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7158</v>
+        <v>0.3301</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5838</v>
+        <v>-0.9376</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1662</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0846</v>
+        <v>-0.7274</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2508</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9409</v>
+        <v>-1.3363</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0257</v>
+        <v>-1.4604</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9152</v>
+        <v>0.1241</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2431</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8399</v>
+        <v>-0.6804</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5968</v>
+        <v>0.1568</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1839</v>
+        <v>-0.8126</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8655</v>
+        <v>-0.78</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3184</v>
+        <v>-0.0326</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8325</v>
+        <v>1.8731</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1097</v>
+        <v>-0.0458</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8416</v>
+        <v>-0.2038</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2682</v>
+        <v>0.1579</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,37 +799,37 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6464</v>
+        <v>-0.3931</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3467</v>
+        <v>0.8284</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9931</v>
+        <v>-1.2215</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3658</v>
+        <v>-0.9409</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1258</v>
+        <v>-0.0257</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.24</v>
+        <v>-0.9152</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7692</v>
+        <v>0.2431</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6908</v>
+        <v>0.8399</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0784</v>
+        <v>-0.5968</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1349</v>
+        <v>-1.1839</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8165</v>
+        <v>-0.8655</v>
       </c>
       <c r="O5" t="n">
         <v>-0.3184</v>
@@ -844,19 +844,19 @@
         <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1755</v>
+        <v>0.8829</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6524</v>
+        <v>0.5853</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4769</v>
+        <v>0.2975</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9376</v>
+        <v>-1.1675</v>
       </c>
       <c r="W5" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-1.1675</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. BERTAIN</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6029</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.5875</v>
+        <v>-0.2072</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9846</v>
+        <v>-0.3084</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5063</v>
+        <v>-1.4934</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1322</v>
+        <v>-1.5032</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6386</v>
+        <v>0.0098</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3512</v>
+        <v>-0.0357</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0384</v>
+        <v>-0.1475</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3896</v>
+        <v>0.1118</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1551</v>
+        <v>-1.4577</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0939</v>
+        <v>-1.3556</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.249</v>
+        <v>-0.102</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4162</v>
+        <v>2.7055</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6244</v>
+        <v>2.7055</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3197</v>
+        <v>-1.144</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1957</v>
+        <v>-0.7552</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5154</v>
+        <v>-0.3888</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>N. BERTAIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9167</v>
+        <v>-1.4217</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.344</v>
+        <v>-2.2008</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5727</v>
+        <v>0.7791</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4934</v>
+        <v>-1.5063</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5032</v>
+        <v>0.1322</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0098</v>
+        <v>-1.6386</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0357</v>
+        <v>-1.3512</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1475</v>
+        <v>0.0384</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1118</v>
+        <v>-1.3896</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4577</v>
+        <v>-0.1551</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3556</v>
+        <v>0.0939</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.102</v>
+        <v>-0.249</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7055</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7055</v>
+        <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.5451</v>
+        <v>0.5009</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.8921</v>
+        <v>0.191</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.653</v>
+        <v>0.3099</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. OKAFOR</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9893</v>
+        <v>-1.577</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7618</v>
+        <v>-2.7178</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2275</v>
+        <v>1.1407</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8725</v>
+        <v>-3.5576</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5566</v>
+        <v>-1.7998</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.316</v>
+        <v>-1.7578</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3704</v>
+        <v>-2.3489</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4096</v>
+        <v>-0.4442</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0392</v>
+        <v>-1.9047</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5022</v>
+        <v>-1.2086</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.147</v>
+        <v>-1.3556</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3551</v>
+        <v>0.147</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2081</v>
+        <v>1.6649</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2081</v>
+        <v>2.7055</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3249</v>
+        <v>-1.0819</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3915</v>
+        <v>-0.7257</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06660000000000001</v>
+        <v>-0.3562</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>O. OKAFOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0518</v>
+        <v>-1.9409</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1045</v>
+        <v>-1.6547</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0527</v>
+        <v>-0.2862</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5576</v>
+        <v>-1.8725</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7998</v>
+        <v>-1.5566</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7578</v>
+        <v>-0.316</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.3489</v>
+        <v>-1.3704</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4442</v>
+        <v>-1.4096</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9047</v>
+        <v>0.0392</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2086</v>
+        <v>-0.5022</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3556</v>
+        <v>-0.147</v>
       </c>
       <c r="O9" t="n">
-        <v>0.147</v>
+        <v>-0.3551</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6649</v>
+        <v>0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7055</v>
+        <v>0.2081</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5567</v>
+        <v>-0.2765</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1124</v>
+        <v>-0.2843</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4442</v>
+        <v>0.0078</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3581</v>
+        <v>-2.0389</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3929</v>
+        <v>-1.2461</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2075</v>
@@ -1234,13 +1234,13 @@
         <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.2882</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.199</v>
+        <v>-0.0266</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4084</v>
+        <v>-0.2616</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1675</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2575</v>
+        <v>-5.1779</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.5793</v>
+        <v>-5.764</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3218</v>
+        <v>0.586</v>
       </c>
       <c r="G11" t="n">
         <v>-5.7192</v>
@@ -1312,13 +1312,13 @@
         <v>2.4974</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4145</v>
+        <v>-0.3349</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7862</v>
+        <v>0.0291</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6282</v>
+        <v>-0.364</v>
       </c>
       <c r="V11" t="n">
         <v>0.4599</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.4454</v>
+        <v>-10.7929</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.916099999999998</v>
+        <v>-8.2638</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5292</v>
+        <v>-2.5293</v>
       </c>
       <c r="G12" t="n">
         <v>-17.6964</v>
@@ -1390,13 +1390,13 @@
         <v>16.6494</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2809000000000006</v>
+        <v>0.3717000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.04940000000000055</v>
+        <v>0.6029000000000003</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2311000000000001</v>
+        <v>-0.2315</v>
       </c>
       <c r="V12" t="n">
         <v>-3.8742</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1832</v>
+        <v>6.5238</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9106</v>
+        <v>7.3392</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.8154</v>
       </c>
       <c r="G13" t="n">
         <v>6.3418</v>
@@ -1468,13 +1468,13 @@
         <v>0.6244</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2231</v>
+        <v>0.1175</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2486</v>
+        <v>0.18</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0255</v>
+        <v>-0.0626</v>
       </c>
       <c r="V13" t="n">
         <v>1.5213</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.507</v>
+        <v>4.78</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8649</v>
+        <v>3.0792</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6421</v>
+        <v>1.7008</v>
       </c>
       <c r="G14" t="n">
         <v>4.5298</v>
@@ -1546,13 +1546,13 @@
         <v>0.4162</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.439</v>
+        <v>-0.166</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5219</v>
+        <v>-0.3076</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0829</v>
+        <v>0.1416</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.933</v>
+        <v>3.3957</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3168</v>
+        <v>1.1025</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6162</v>
+        <v>2.2932</v>
       </c>
       <c r="G15" t="n">
         <v>5.1483</v>
@@ -1624,13 +1624,13 @@
         <v>0.6244</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7014</v>
+        <v>0.1641</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0033</v>
+        <v>-0.2176</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7047</v>
+        <v>0.3818</v>
       </c>
       <c r="V15" t="n">
         <v>-0.4599</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2314</v>
+        <v>3.1815</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6766</v>
+        <v>1.8909</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5548</v>
+        <v>1.2906</v>
       </c>
       <c r="G16" t="n">
         <v>1.8019</v>
@@ -1702,13 +1702,13 @@
         <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9082</v>
+        <v>0.8583</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2048</v>
+        <v>0.4191</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7034</v>
+        <v>0.4391</v>
       </c>
       <c r="V16" t="n">
         <v>0.9376</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8296</v>
+        <v>2.0238</v>
       </c>
       <c r="E17" t="n">
-        <v>1.511</v>
+        <v>1.6582</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3186</v>
+        <v>0.3656</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1067</v>
+        <v>0.2396</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3622</v>
+        <v>0.3114</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2555</v>
+        <v>-0.0718</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0732</v>
+        <v>0.3092</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7483</v>
+        <v>0.279</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6752</v>
+        <v>0.0302</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1798</v>
+        <v>-0.0696</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1106</v>
+        <v>0.0324</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9307</v>
+        <v>-0.102</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6244</v>
+        <v>0.6244</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5607</v>
+        <v>-0.0076</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4784</v>
+        <v>0.1815</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0823</v>
+        <v>-0.1891</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>L. SORENSEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7992</v>
+        <v>0.5812</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5511</v>
+        <v>-0.3729</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2482</v>
+        <v>0.9542</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2396</v>
+        <v>1.8415</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3114</v>
+        <v>0.7655</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0718</v>
+        <v>1.0761</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3092</v>
+        <v>1.1477</v>
       </c>
       <c r="K18" t="n">
-        <v>0.279</v>
+        <v>1.1085</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0302</v>
+        <v>0.0392</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0696</v>
+        <v>0.6938</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0324</v>
+        <v>-0.3431</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.102</v>
+        <v>1.0369</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6244</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2322</v>
+        <v>-0.844</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0743</v>
+        <v>-0.48</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3066</v>
+        <v>-0.364</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. SORENSEN</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3273</v>
+        <v>0.2707</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4801</v>
+        <v>0.0108</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8074</v>
+        <v>0.2599</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8415</v>
+        <v>-0.1067</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7655</v>
+        <v>-0.3622</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0761</v>
+        <v>0.2555</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1477</v>
+        <v>0.0732</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1085</v>
+        <v>0.7483</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0392</v>
+        <v>-0.6752</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6938</v>
+        <v>-0.1798</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3431</v>
+        <v>-1.1106</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0369</v>
+        <v>0.9307</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4162</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.098</v>
+        <v>1.0018</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.9782</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5108</v>
+        <v>0.0235</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1409</v>
+        <v>-0.0234</v>
       </c>
       <c r="E20" t="n">
         <v>-1.9474</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8065</v>
+        <v>1.924</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2096</v>
@@ -2014,13 +2014,13 @@
         <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.077</v>
+        <v>0.0405</v>
       </c>
       <c r="T20" t="n">
         <v>0.2701</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.347</v>
+        <v>-0.2296</v>
       </c>
       <c r="V20" t="n">
         <v>0.3538</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5048</v>
+        <v>-1.1437</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2254</v>
+        <v>-1.0111</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2794</v>
+        <v>-0.1326</v>
       </c>
       <c r="G21" t="n">
         <v>0.3204</v>
@@ -2092,13 +2092,13 @@
         <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5141</v>
+        <v>-0.153</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3915</v>
+        <v>-0.1771</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1226</v>
+        <v>0.0242</v>
       </c>
       <c r="V21" t="n">
         <v>0.3538</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7245</v>
+        <v>-1.8126</v>
       </c>
       <c r="E22" t="n">
         <v>-2.4693</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7448</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5758</v>
@@ -2170,13 +2170,13 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.6531</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3262</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2388</v>
+        <v>-0.3268</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9952</v>
+        <v>-6.3317</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.1795</v>
+        <v>-6.7509</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1843</v>
+        <v>0.4192</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6349</v>
@@ -2248,13 +2248,13 @@
         <v>0.6244</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7411</v>
+        <v>-0.0776</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7177</v>
+        <v>-0.2891</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0235</v>
+        <v>0.2114</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2284,10 +2284,10 @@
         <v>11.4453</v>
       </c>
       <c r="E24" t="n">
-        <v>2.529299999999997</v>
+        <v>2.529199999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>8.916200000000002</v>
+        <v>8.9163</v>
       </c>
       <c r="G24" t="n">
         <v>17.6963</v>
@@ -2305,10 +2305,10 @@
         <v>8.227499999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>3.7147</v>
+        <v>3.714699999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>5.7542</v>
+        <v>5.754200000000001</v>
       </c>
       <c r="N24" t="n">
         <v>0.3655999999999995</v>
@@ -2326,13 +2326,13 @@
         <v>6.243699999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2808</v>
+        <v>0.2809</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2312000000000003</v>
+        <v>0.2313</v>
       </c>
       <c r="U24" t="n">
-        <v>0.04950000000000012</v>
+        <v>0.04950000000000007</v>
       </c>
       <c r="V24" t="n">
         <v>3.8741</v>
